--- a/test_results/gemini_3_pro_preview_11_2025/统计表格.xlsx
+++ b/test_results/gemini_3_pro_preview_11_2025/统计表格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\111\LLM-NeedleInAHaystack\test_results\gemini_3_pro_preview_11_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{374CE123-594E-43F0-BD0A-682E025B3941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD7670F-2422-4DEB-B3B2-59A0AE0B28B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{58898F7C-67C2-4EC0-A511-F699C1A6044A}"/>
   </bookViews>
@@ -320,43 +320,43 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>98.09</c:v>
+                  <c:v>99.76</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>91.33</c:v>
+                  <c:v>93.92</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>75.27</c:v>
+                  <c:v>89.55</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46.55</c:v>
+                  <c:v>72.41</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>19.71</c:v>
+                  <c:v>46.06</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>16.670000000000002</c:v>
+                  <c:v>36.479999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>10.31</c:v>
+                  <c:v>32.29</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9.26</c:v>
+                  <c:v>23.75</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.77</c:v>
+                  <c:v>22.95</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9.3800000000000008</c:v>
+                  <c:v>22.77</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6.67</c:v>
+                  <c:v>19.36</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.8899999999999997</c:v>
+                  <c:v>18.11</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.13</c:v>
+                  <c:v>15.05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1475,43 +1475,43 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>98.09</c:v>
+                  <c:v>99.76</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>91.33</c:v>
+                  <c:v>93.92</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>75.27</c:v>
+                  <c:v>89.55</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46.55</c:v>
+                  <c:v>72.41</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>19.71</c:v>
+                  <c:v>46.06</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>16.670000000000002</c:v>
+                  <c:v>36.479999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>10.31</c:v>
+                  <c:v>32.29</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9.26</c:v>
+                  <c:v>23.75</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.77</c:v>
+                  <c:v>22.95</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9.3800000000000008</c:v>
+                  <c:v>22.77</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6.67</c:v>
+                  <c:v>19.36</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.8899999999999997</c:v>
+                  <c:v>18.11</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.13</c:v>
+                  <c:v>15.05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3599,16 +3599,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>311150</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>260350</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4085,43 +4085,43 @@
         <v>100</v>
       </c>
       <c r="D8">
-        <v>98.09</v>
+        <v>99.76</v>
       </c>
       <c r="E8">
-        <v>91.33</v>
+        <v>93.92</v>
       </c>
       <c r="F8">
-        <v>75.27</v>
+        <v>89.55</v>
       </c>
       <c r="G8">
-        <v>46.55</v>
+        <v>72.41</v>
       </c>
       <c r="H8">
-        <v>19.71</v>
+        <v>46.06</v>
       </c>
       <c r="I8">
-        <v>16.670000000000002</v>
+        <v>36.479999999999997</v>
       </c>
       <c r="J8">
-        <v>10.31</v>
+        <v>32.29</v>
       </c>
       <c r="K8">
-        <v>9.26</v>
+        <v>23.75</v>
       </c>
       <c r="L8">
-        <v>7.77</v>
+        <v>22.95</v>
       </c>
       <c r="M8">
-        <v>9.3800000000000008</v>
+        <v>22.77</v>
       </c>
       <c r="N8">
-        <v>6.67</v>
+        <v>19.36</v>
       </c>
       <c r="O8">
-        <v>4.8899999999999997</v>
+        <v>18.11</v>
       </c>
       <c r="P8">
-        <v>3.13</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
